--- a/Leitor_de_Fatura/Faturas_Analaiser/Relatorio_Consolidado_RIBEIRAO_Texter.xlsx
+++ b/Leitor_de_Fatura/Faturas_Analaiser/Relatorio_Consolidado_RIBEIRAO_Texter.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Base_Vazia" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Classificação" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Consumo_Faturado" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Consumo_Medido" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -429,18 +429,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,18 +516,64 @@
           <t>3314094</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
-      <c r="G2" s="1" t="inlineStr"/>
-      <c r="H2" s="1" t="inlineStr"/>
-      <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr"/>
-      <c r="K2" s="1" t="inlineStr"/>
-      <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="B2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -535,18 +581,64 @@
           <t>3315598</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr"/>
-      <c r="D3" s="1" t="inlineStr"/>
-      <c r="E3" s="1" t="inlineStr"/>
-      <c r="F3" s="1" t="inlineStr"/>
-      <c r="G3" s="1" t="inlineStr"/>
-      <c r="H3" s="1" t="inlineStr"/>
-      <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr"/>
-      <c r="L3" s="1" t="inlineStr"/>
-      <c r="M3" s="1" t="inlineStr"/>
+      <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -554,18 +646,64 @@
           <t>3315670</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" s="1" t="inlineStr"/>
-      <c r="D4" s="1" t="inlineStr"/>
-      <c r="E4" s="1" t="inlineStr"/>
-      <c r="F4" s="1" t="inlineStr"/>
-      <c r="G4" s="1" t="inlineStr"/>
-      <c r="H4" s="1" t="inlineStr"/>
-      <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr"/>
-      <c r="L4" s="1" t="inlineStr"/>
-      <c r="M4" s="1" t="inlineStr"/>
+      <c r="B4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -573,18 +711,64 @@
           <t>3315672</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr"/>
-      <c r="D5" s="1" t="inlineStr"/>
-      <c r="E5" s="1" t="inlineStr"/>
-      <c r="F5" s="1" t="inlineStr"/>
-      <c r="G5" s="1" t="inlineStr"/>
-      <c r="H5" s="1" t="inlineStr"/>
-      <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr"/>
-      <c r="L5" s="1" t="inlineStr"/>
-      <c r="M5" s="1" t="inlineStr"/>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -592,18 +776,58 @@
           <t>3315727</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr"/>
-      <c r="D6" s="1" t="inlineStr"/>
-      <c r="E6" s="1" t="inlineStr"/>
-      <c r="F6" s="1" t="inlineStr"/>
-      <c r="G6" s="1" t="inlineStr"/>
-      <c r="H6" s="1" t="inlineStr"/>
-      <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr"/>
-      <c r="L6" s="1" t="inlineStr"/>
-      <c r="M6" s="1" t="inlineStr"/>
+      <c r="B6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -611,18 +835,64 @@
           <t>3315728</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr"/>
-      <c r="F7" s="1" t="inlineStr"/>
-      <c r="G7" s="1" t="inlineStr"/>
-      <c r="H7" s="1" t="inlineStr"/>
-      <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr"/>
-      <c r="L7" s="1" t="inlineStr"/>
-      <c r="M7" s="1" t="inlineStr"/>
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -630,18 +900,64 @@
           <t>3315729</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr"/>
-      <c r="D8" s="1" t="inlineStr"/>
-      <c r="E8" s="1" t="inlineStr"/>
-      <c r="F8" s="1" t="inlineStr"/>
-      <c r="G8" s="1" t="inlineStr"/>
-      <c r="H8" s="1" t="inlineStr"/>
-      <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr"/>
-      <c r="L8" s="1" t="inlineStr"/>
-      <c r="M8" s="1" t="inlineStr"/>
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -649,18 +965,64 @@
           <t>3315786</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr"/>
-      <c r="D9" s="1" t="inlineStr"/>
-      <c r="E9" s="1" t="inlineStr"/>
-      <c r="F9" s="1" t="inlineStr"/>
-      <c r="G9" s="1" t="inlineStr"/>
-      <c r="H9" s="1" t="inlineStr"/>
-      <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr"/>
-      <c r="L9" s="1" t="inlineStr"/>
-      <c r="M9" s="1" t="inlineStr"/>
+      <c r="B9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -668,18 +1030,64 @@
           <t>3315795</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr"/>
-      <c r="D10" s="1" t="inlineStr"/>
-      <c r="E10" s="1" t="inlineStr"/>
-      <c r="F10" s="1" t="inlineStr"/>
-      <c r="G10" s="1" t="inlineStr"/>
-      <c r="H10" s="1" t="inlineStr"/>
-      <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr"/>
-      <c r="L10" s="1" t="inlineStr"/>
-      <c r="M10" s="1" t="inlineStr"/>
+      <c r="B10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -687,18 +1095,64 @@
           <t>3315835</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr"/>
-      <c r="D11" s="1" t="inlineStr"/>
-      <c r="E11" s="1" t="inlineStr"/>
-      <c r="F11" s="1" t="inlineStr"/>
-      <c r="G11" s="1" t="inlineStr"/>
-      <c r="H11" s="1" t="inlineStr"/>
-      <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr"/>
-      <c r="L11" s="1" t="inlineStr"/>
-      <c r="M11" s="1" t="inlineStr"/>
+      <c r="B11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -706,18 +1160,64 @@
           <t>3315965</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr"/>
-      <c r="C12" s="1" t="inlineStr"/>
-      <c r="D12" s="1" t="inlineStr"/>
-      <c r="E12" s="1" t="inlineStr"/>
-      <c r="F12" s="1" t="inlineStr"/>
-      <c r="G12" s="1" t="inlineStr"/>
-      <c r="H12" s="1" t="inlineStr"/>
-      <c r="I12" s="1" t="inlineStr"/>
-      <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr"/>
-      <c r="L12" s="1" t="inlineStr"/>
-      <c r="M12" s="1" t="inlineStr"/>
+      <c r="B12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -725,18 +1225,64 @@
           <t>3316090</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr"/>
-      <c r="D13" s="1" t="inlineStr"/>
-      <c r="E13" s="1" t="inlineStr"/>
-      <c r="F13" s="1" t="inlineStr"/>
-      <c r="G13" s="1" t="inlineStr"/>
-      <c r="H13" s="1" t="inlineStr"/>
-      <c r="I13" s="1" t="inlineStr"/>
-      <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr"/>
-      <c r="L13" s="1" t="inlineStr"/>
-      <c r="M13" s="1" t="inlineStr"/>
+      <c r="B13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -744,18 +1290,64 @@
           <t>3316232</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr"/>
-      <c r="D14" s="1" t="inlineStr"/>
-      <c r="E14" s="1" t="inlineStr"/>
-      <c r="F14" s="1" t="inlineStr"/>
-      <c r="G14" s="1" t="inlineStr"/>
-      <c r="H14" s="1" t="inlineStr"/>
-      <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr"/>
-      <c r="L14" s="1" t="inlineStr"/>
-      <c r="M14" s="1" t="inlineStr"/>
+      <c r="B14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L14" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -763,18 +1355,64 @@
           <t>3316233</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr"/>
-      <c r="D15" s="1" t="inlineStr"/>
-      <c r="E15" s="1" t="inlineStr"/>
-      <c r="F15" s="1" t="inlineStr"/>
-      <c r="G15" s="1" t="inlineStr"/>
-      <c r="H15" s="1" t="inlineStr"/>
-      <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr"/>
-      <c r="L15" s="1" t="inlineStr"/>
-      <c r="M15" s="1" t="inlineStr"/>
+      <c r="B15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L15" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -782,18 +1420,64 @@
           <t>3316362</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr"/>
-      <c r="D16" s="1" t="inlineStr"/>
-      <c r="E16" s="1" t="inlineStr"/>
-      <c r="F16" s="1" t="inlineStr"/>
-      <c r="G16" s="1" t="inlineStr"/>
-      <c r="H16" s="1" t="inlineStr"/>
-      <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr"/>
-      <c r="L16" s="1" t="inlineStr"/>
-      <c r="M16" s="1" t="inlineStr"/>
+      <c r="B16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -801,18 +1485,64 @@
           <t>3316376</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr"/>
-      <c r="C17" s="1" t="inlineStr"/>
-      <c r="D17" s="1" t="inlineStr"/>
-      <c r="E17" s="1" t="inlineStr"/>
-      <c r="F17" s="1" t="inlineStr"/>
-      <c r="G17" s="1" t="inlineStr"/>
-      <c r="H17" s="1" t="inlineStr"/>
-      <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr"/>
-      <c r="L17" s="1" t="inlineStr"/>
-      <c r="M17" s="1" t="inlineStr"/>
+      <c r="B17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L17" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M17" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -820,18 +1550,64 @@
           <t>3316503</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr"/>
-      <c r="D18" s="1" t="inlineStr"/>
-      <c r="E18" s="1" t="inlineStr"/>
-      <c r="F18" s="1" t="inlineStr"/>
-      <c r="G18" s="1" t="inlineStr"/>
-      <c r="H18" s="1" t="inlineStr"/>
-      <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr"/>
-      <c r="L18" s="1" t="inlineStr"/>
-      <c r="M18" s="1" t="inlineStr"/>
+      <c r="B18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -839,18 +1615,64 @@
           <t>3316504</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr"/>
-      <c r="D19" s="1" t="inlineStr"/>
-      <c r="E19" s="1" t="inlineStr"/>
-      <c r="F19" s="1" t="inlineStr"/>
-      <c r="G19" s="1" t="inlineStr"/>
-      <c r="H19" s="1" t="inlineStr"/>
-      <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr"/>
-      <c r="L19" s="1" t="inlineStr"/>
-      <c r="M19" s="1" t="inlineStr"/>
+      <c r="B19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L19" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M19" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -858,18 +1680,64 @@
           <t>3316517</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr"/>
-      <c r="D20" s="1" t="inlineStr"/>
-      <c r="E20" s="1" t="inlineStr"/>
-      <c r="F20" s="1" t="inlineStr"/>
-      <c r="G20" s="1" t="inlineStr"/>
-      <c r="H20" s="1" t="inlineStr"/>
-      <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr"/>
-      <c r="L20" s="1" t="inlineStr"/>
-      <c r="M20" s="1" t="inlineStr"/>
+      <c r="B20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -877,18 +1745,64 @@
           <t>3316724</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr"/>
-      <c r="D21" s="1" t="inlineStr"/>
-      <c r="E21" s="1" t="inlineStr"/>
-      <c r="F21" s="1" t="inlineStr"/>
-      <c r="G21" s="1" t="inlineStr"/>
-      <c r="H21" s="1" t="inlineStr"/>
-      <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr"/>
-      <c r="L21" s="1" t="inlineStr"/>
-      <c r="M21" s="1" t="inlineStr"/>
+      <c r="B21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L21" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M21" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -896,18 +1810,64 @@
           <t>3316726</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr"/>
-      <c r="D22" s="1" t="inlineStr"/>
-      <c r="E22" s="1" t="inlineStr"/>
-      <c r="F22" s="1" t="inlineStr"/>
-      <c r="G22" s="1" t="inlineStr"/>
-      <c r="H22" s="1" t="inlineStr"/>
-      <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr"/>
-      <c r="L22" s="1" t="inlineStr"/>
-      <c r="M22" s="1" t="inlineStr"/>
+      <c r="B22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L22" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M22" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -915,18 +1875,64 @@
           <t>3316831</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr"/>
-      <c r="D23" s="1" t="inlineStr"/>
-      <c r="E23" s="1" t="inlineStr"/>
-      <c r="F23" s="1" t="inlineStr"/>
-      <c r="G23" s="1" t="inlineStr"/>
-      <c r="H23" s="1" t="inlineStr"/>
-      <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr"/>
-      <c r="L23" s="1" t="inlineStr"/>
-      <c r="M23" s="1" t="inlineStr"/>
+      <c r="B23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J23" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L23" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M23" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -934,18 +1940,64 @@
           <t>3317459</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr"/>
-      <c r="D24" s="1" t="inlineStr"/>
-      <c r="E24" s="1" t="inlineStr"/>
-      <c r="F24" s="1" t="inlineStr"/>
-      <c r="G24" s="1" t="inlineStr"/>
-      <c r="H24" s="1" t="inlineStr"/>
-      <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr"/>
-      <c r="L24" s="1" t="inlineStr"/>
-      <c r="M24" s="1" t="inlineStr"/>
+      <c r="B24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J24" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K24" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L24" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M24" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -953,18 +2005,64 @@
           <t>3317594</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr"/>
-      <c r="D25" s="1" t="inlineStr"/>
-      <c r="E25" s="1" t="inlineStr"/>
-      <c r="F25" s="1" t="inlineStr"/>
-      <c r="G25" s="1" t="inlineStr"/>
-      <c r="H25" s="1" t="inlineStr"/>
-      <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr"/>
-      <c r="L25" s="1" t="inlineStr"/>
-      <c r="M25" s="1" t="inlineStr"/>
+      <c r="B25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K25" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L25" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M25" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -972,18 +2070,64 @@
           <t>3317741</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr"/>
-      <c r="D26" s="1" t="inlineStr"/>
-      <c r="E26" s="1" t="inlineStr"/>
-      <c r="F26" s="1" t="inlineStr"/>
-      <c r="G26" s="1" t="inlineStr"/>
-      <c r="H26" s="1" t="inlineStr"/>
-      <c r="I26" s="1" t="inlineStr"/>
-      <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr"/>
-      <c r="L26" s="1" t="inlineStr"/>
-      <c r="M26" s="1" t="inlineStr"/>
+      <c r="B26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J26" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K26" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L26" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M26" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -991,18 +2135,64 @@
           <t>3317746</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="1" t="inlineStr"/>
-      <c r="D27" s="1" t="inlineStr"/>
-      <c r="E27" s="1" t="inlineStr"/>
-      <c r="F27" s="1" t="inlineStr"/>
-      <c r="G27" s="1" t="inlineStr"/>
-      <c r="H27" s="1" t="inlineStr"/>
-      <c r="I27" s="1" t="inlineStr"/>
-      <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr"/>
-      <c r="L27" s="1" t="inlineStr"/>
-      <c r="M27" s="1" t="inlineStr"/>
+      <c r="B27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J27" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K27" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L27" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M27" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1010,18 +2200,64 @@
           <t>3317749</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr"/>
-      <c r="D28" s="1" t="inlineStr"/>
-      <c r="E28" s="1" t="inlineStr"/>
-      <c r="F28" s="1" t="inlineStr"/>
-      <c r="G28" s="1" t="inlineStr"/>
-      <c r="H28" s="1" t="inlineStr"/>
-      <c r="I28" s="1" t="inlineStr"/>
-      <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr"/>
-      <c r="L28" s="1" t="inlineStr"/>
-      <c r="M28" s="1" t="inlineStr"/>
+      <c r="B28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L28" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M28" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1029,18 +2265,64 @@
           <t>3317750</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" s="1" t="inlineStr"/>
-      <c r="D29" s="1" t="inlineStr"/>
-      <c r="E29" s="1" t="inlineStr"/>
-      <c r="F29" s="1" t="inlineStr"/>
-      <c r="G29" s="1" t="inlineStr"/>
-      <c r="H29" s="1" t="inlineStr"/>
-      <c r="I29" s="1" t="inlineStr"/>
-      <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr"/>
-      <c r="L29" s="1" t="inlineStr"/>
-      <c r="M29" s="1" t="inlineStr"/>
+      <c r="B29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J29" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K29" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L29" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M29" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -1048,18 +2330,64 @@
           <t>3317752</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr"/>
-      <c r="C30" s="1" t="inlineStr"/>
-      <c r="D30" s="1" t="inlineStr"/>
-      <c r="E30" s="1" t="inlineStr"/>
-      <c r="F30" s="1" t="inlineStr"/>
-      <c r="G30" s="1" t="inlineStr"/>
-      <c r="H30" s="1" t="inlineStr"/>
-      <c r="I30" s="1" t="inlineStr"/>
-      <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr"/>
-      <c r="L30" s="1" t="inlineStr"/>
-      <c r="M30" s="1" t="inlineStr"/>
+      <c r="B30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J30" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L30" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M30" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -1067,18 +2395,64 @@
           <t>3317753</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr"/>
-      <c r="C31" s="1" t="inlineStr"/>
-      <c r="D31" s="1" t="inlineStr"/>
-      <c r="E31" s="1" t="inlineStr"/>
-      <c r="F31" s="1" t="inlineStr"/>
-      <c r="G31" s="1" t="inlineStr"/>
-      <c r="H31" s="1" t="inlineStr"/>
-      <c r="I31" s="1" t="inlineStr"/>
-      <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr"/>
-      <c r="L31" s="1" t="inlineStr"/>
-      <c r="M31" s="1" t="inlineStr"/>
+      <c r="B31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K31" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L31" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M31" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1086,18 +2460,64 @@
           <t>3317754</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr"/>
-      <c r="C32" s="1" t="inlineStr"/>
-      <c r="D32" s="1" t="inlineStr"/>
-      <c r="E32" s="1" t="inlineStr"/>
-      <c r="F32" s="1" t="inlineStr"/>
-      <c r="G32" s="1" t="inlineStr"/>
-      <c r="H32" s="1" t="inlineStr"/>
-      <c r="I32" s="1" t="inlineStr"/>
-      <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr"/>
-      <c r="L32" s="1" t="inlineStr"/>
-      <c r="M32" s="1" t="inlineStr"/>
+      <c r="B32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L32" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M32" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1105,18 +2525,64 @@
           <t>3317756</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr"/>
-      <c r="C33" s="1" t="inlineStr"/>
-      <c r="D33" s="1" t="inlineStr"/>
-      <c r="E33" s="1" t="inlineStr"/>
-      <c r="F33" s="1" t="inlineStr"/>
-      <c r="G33" s="1" t="inlineStr"/>
-      <c r="H33" s="1" t="inlineStr"/>
-      <c r="I33" s="1" t="inlineStr"/>
-      <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr"/>
-      <c r="L33" s="1" t="inlineStr"/>
-      <c r="M33" s="1" t="inlineStr"/>
+      <c r="B33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J33" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K33" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L33" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M33" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1124,18 +2590,64 @@
           <t>3317759</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr"/>
-      <c r="C34" s="1" t="inlineStr"/>
-      <c r="D34" s="1" t="inlineStr"/>
-      <c r="E34" s="1" t="inlineStr"/>
-      <c r="F34" s="1" t="inlineStr"/>
-      <c r="G34" s="1" t="inlineStr"/>
-      <c r="H34" s="1" t="inlineStr"/>
-      <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr"/>
-      <c r="L34" s="1" t="inlineStr"/>
-      <c r="M34" s="1" t="inlineStr"/>
+      <c r="B34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J34" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K34" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L34" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M34" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1143,18 +2655,64 @@
           <t>3317762</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr"/>
-      <c r="C35" s="1" t="inlineStr"/>
-      <c r="D35" s="1" t="inlineStr"/>
-      <c r="E35" s="1" t="inlineStr"/>
-      <c r="F35" s="1" t="inlineStr"/>
-      <c r="G35" s="1" t="inlineStr"/>
-      <c r="H35" s="1" t="inlineStr"/>
-      <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr"/>
-      <c r="L35" s="1" t="inlineStr"/>
-      <c r="M35" s="1" t="inlineStr"/>
+      <c r="B35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J35" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K35" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L35" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M35" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1162,18 +2720,64 @@
           <t>3317798</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr"/>
-      <c r="C36" s="1" t="inlineStr"/>
-      <c r="D36" s="1" t="inlineStr"/>
-      <c r="E36" s="1" t="inlineStr"/>
-      <c r="F36" s="1" t="inlineStr"/>
-      <c r="G36" s="1" t="inlineStr"/>
-      <c r="H36" s="1" t="inlineStr"/>
-      <c r="I36" s="1" t="inlineStr"/>
-      <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr"/>
-      <c r="L36" s="1" t="inlineStr"/>
-      <c r="M36" s="1" t="inlineStr"/>
+      <c r="B36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J36" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K36" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L36" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M36" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1181,18 +2785,64 @@
           <t>3317799</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr"/>
-      <c r="C37" s="1" t="inlineStr"/>
-      <c r="D37" s="1" t="inlineStr"/>
-      <c r="E37" s="1" t="inlineStr"/>
-      <c r="F37" s="1" t="inlineStr"/>
-      <c r="G37" s="1" t="inlineStr"/>
-      <c r="H37" s="1" t="inlineStr"/>
-      <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr"/>
-      <c r="L37" s="1" t="inlineStr"/>
-      <c r="M37" s="1" t="inlineStr"/>
+      <c r="B37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I37" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J37" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K37" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L37" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M37" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1200,18 +2850,64 @@
           <t>3317848</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr"/>
-      <c r="C38" s="1" t="inlineStr"/>
-      <c r="D38" s="1" t="inlineStr"/>
-      <c r="E38" s="1" t="inlineStr"/>
-      <c r="F38" s="1" t="inlineStr"/>
-      <c r="G38" s="1" t="inlineStr"/>
-      <c r="H38" s="1" t="inlineStr"/>
-      <c r="I38" s="1" t="inlineStr"/>
-      <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr"/>
-      <c r="L38" s="1" t="inlineStr"/>
-      <c r="M38" s="1" t="inlineStr"/>
+      <c r="B38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H38" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K38" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L38" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M38" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1219,18 +2915,64 @@
           <t>3318220</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr"/>
-      <c r="C39" s="1" t="inlineStr"/>
-      <c r="D39" s="1" t="inlineStr"/>
-      <c r="E39" s="1" t="inlineStr"/>
-      <c r="F39" s="1" t="inlineStr"/>
-      <c r="G39" s="1" t="inlineStr"/>
-      <c r="H39" s="1" t="inlineStr"/>
-      <c r="I39" s="1" t="inlineStr"/>
-      <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr"/>
-      <c r="L39" s="1" t="inlineStr"/>
-      <c r="M39" s="1" t="inlineStr"/>
+      <c r="B39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I39" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J39" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K39" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L39" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M39" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -1238,18 +2980,64 @@
           <t>3318674</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr"/>
-      <c r="C40" s="1" t="inlineStr"/>
-      <c r="D40" s="1" t="inlineStr"/>
-      <c r="E40" s="1" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr"/>
-      <c r="G40" s="1" t="inlineStr"/>
-      <c r="H40" s="1" t="inlineStr"/>
-      <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr"/>
-      <c r="L40" s="1" t="inlineStr"/>
-      <c r="M40" s="1" t="inlineStr"/>
+      <c r="B40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H40" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I40" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J40" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K40" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L40" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M40" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -1257,18 +3045,64 @@
           <t>3318688</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr"/>
-      <c r="C41" s="1" t="inlineStr"/>
-      <c r="D41" s="1" t="inlineStr"/>
-      <c r="E41" s="1" t="inlineStr"/>
-      <c r="F41" s="1" t="inlineStr"/>
-      <c r="G41" s="1" t="inlineStr"/>
-      <c r="H41" s="1" t="inlineStr"/>
-      <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr"/>
-      <c r="L41" s="1" t="inlineStr"/>
-      <c r="M41" s="1" t="inlineStr"/>
+      <c r="B41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J41" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K41" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L41" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M41" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -1276,18 +3110,64 @@
           <t>3318701</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr"/>
-      <c r="C42" s="1" t="inlineStr"/>
-      <c r="D42" s="1" t="inlineStr"/>
-      <c r="E42" s="1" t="inlineStr"/>
-      <c r="F42" s="1" t="inlineStr"/>
-      <c r="G42" s="1" t="inlineStr"/>
-      <c r="H42" s="1" t="inlineStr"/>
-      <c r="I42" s="1" t="inlineStr"/>
-      <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr"/>
-      <c r="L42" s="1" t="inlineStr"/>
-      <c r="M42" s="1" t="inlineStr"/>
+      <c r="B42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I42" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J42" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K42" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L42" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M42" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -1295,18 +3175,64 @@
           <t>3319394</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr"/>
-      <c r="C43" s="1" t="inlineStr"/>
-      <c r="D43" s="1" t="inlineStr"/>
-      <c r="E43" s="1" t="inlineStr"/>
-      <c r="F43" s="1" t="inlineStr"/>
-      <c r="G43" s="1" t="inlineStr"/>
-      <c r="H43" s="1" t="inlineStr"/>
-      <c r="I43" s="1" t="inlineStr"/>
-      <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr"/>
-      <c r="L43" s="1" t="inlineStr"/>
-      <c r="M43" s="1" t="inlineStr"/>
+      <c r="B43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J43" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K43" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L43" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M43" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1314,18 +3240,64 @@
           <t>3319409</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr"/>
-      <c r="C44" s="1" t="inlineStr"/>
-      <c r="D44" s="1" t="inlineStr"/>
-      <c r="E44" s="1" t="inlineStr"/>
-      <c r="F44" s="1" t="inlineStr"/>
-      <c r="G44" s="1" t="inlineStr"/>
-      <c r="H44" s="1" t="inlineStr"/>
-      <c r="I44" s="1" t="inlineStr"/>
-      <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr"/>
-      <c r="L44" s="1" t="inlineStr"/>
-      <c r="M44" s="1" t="inlineStr"/>
+      <c r="B44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I44" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J44" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K44" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L44" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M44" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -1333,18 +3305,64 @@
           <t>3319603</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr"/>
-      <c r="C45" s="1" t="inlineStr"/>
-      <c r="D45" s="1" t="inlineStr"/>
-      <c r="E45" s="1" t="inlineStr"/>
-      <c r="F45" s="1" t="inlineStr"/>
-      <c r="G45" s="1" t="inlineStr"/>
-      <c r="H45" s="1" t="inlineStr"/>
-      <c r="I45" s="1" t="inlineStr"/>
-      <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr"/>
-      <c r="L45" s="1" t="inlineStr"/>
-      <c r="M45" s="1" t="inlineStr"/>
+      <c r="B45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H45" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I45" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J45" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K45" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L45" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M45" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -1352,18 +3370,64 @@
           <t>3319605</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr"/>
-      <c r="C46" s="1" t="inlineStr"/>
-      <c r="D46" s="1" t="inlineStr"/>
-      <c r="E46" s="1" t="inlineStr"/>
-      <c r="F46" s="1" t="inlineStr"/>
-      <c r="G46" s="1" t="inlineStr"/>
-      <c r="H46" s="1" t="inlineStr"/>
-      <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr"/>
-      <c r="L46" s="1" t="inlineStr"/>
-      <c r="M46" s="1" t="inlineStr"/>
+      <c r="B46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H46" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I46" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J46" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K46" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L46" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M46" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -1371,18 +3435,64 @@
           <t>3319606</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr"/>
-      <c r="C47" s="1" t="inlineStr"/>
-      <c r="D47" s="1" t="inlineStr"/>
-      <c r="E47" s="1" t="inlineStr"/>
-      <c r="F47" s="1" t="inlineStr"/>
-      <c r="G47" s="1" t="inlineStr"/>
-      <c r="H47" s="1" t="inlineStr"/>
-      <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr"/>
-      <c r="L47" s="1" t="inlineStr"/>
-      <c r="M47" s="1" t="inlineStr"/>
+      <c r="B47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I47" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J47" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K47" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L47" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M47" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -1390,18 +3500,64 @@
           <t>3319609</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr"/>
-      <c r="C48" s="1" t="inlineStr"/>
-      <c r="D48" s="1" t="inlineStr"/>
-      <c r="E48" s="1" t="inlineStr"/>
-      <c r="F48" s="1" t="inlineStr"/>
-      <c r="G48" s="1" t="inlineStr"/>
-      <c r="H48" s="1" t="inlineStr"/>
-      <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr"/>
-      <c r="L48" s="1" t="inlineStr"/>
-      <c r="M48" s="1" t="inlineStr"/>
+      <c r="B48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I48" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J48" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K48" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L48" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M48" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -1409,18 +3565,64 @@
           <t>3319642</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr"/>
-      <c r="C49" s="1" t="inlineStr"/>
-      <c r="D49" s="1" t="inlineStr"/>
-      <c r="E49" s="1" t="inlineStr"/>
-      <c r="F49" s="1" t="inlineStr"/>
-      <c r="G49" s="1" t="inlineStr"/>
-      <c r="H49" s="1" t="inlineStr"/>
-      <c r="I49" s="1" t="inlineStr"/>
-      <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr"/>
-      <c r="L49" s="1" t="inlineStr"/>
-      <c r="M49" s="1" t="inlineStr"/>
+      <c r="B49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J49" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K49" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L49" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M49" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -1428,18 +3630,64 @@
           <t>3319708</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr"/>
-      <c r="C50" s="1" t="inlineStr"/>
-      <c r="D50" s="1" t="inlineStr"/>
-      <c r="E50" s="1" t="inlineStr"/>
-      <c r="F50" s="1" t="inlineStr"/>
-      <c r="G50" s="1" t="inlineStr"/>
-      <c r="H50" s="1" t="inlineStr"/>
-      <c r="I50" s="1" t="inlineStr"/>
-      <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr"/>
-      <c r="L50" s="1" t="inlineStr"/>
-      <c r="M50" s="1" t="inlineStr"/>
+      <c r="B50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I50" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J50" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K50" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L50" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M50" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -1447,18 +3695,64 @@
           <t>3319729</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr"/>
-      <c r="C51" s="1" t="inlineStr"/>
-      <c r="D51" s="1" t="inlineStr"/>
-      <c r="E51" s="1" t="inlineStr"/>
-      <c r="F51" s="1" t="inlineStr"/>
-      <c r="G51" s="1" t="inlineStr"/>
-      <c r="H51" s="1" t="inlineStr"/>
-      <c r="I51" s="1" t="inlineStr"/>
-      <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr"/>
-      <c r="L51" s="1" t="inlineStr"/>
-      <c r="M51" s="1" t="inlineStr"/>
+      <c r="B51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H51" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J51" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K51" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L51" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M51" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -1466,18 +3760,64 @@
           <t>3320737</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr"/>
-      <c r="C52" s="1" t="inlineStr"/>
-      <c r="D52" s="1" t="inlineStr"/>
-      <c r="E52" s="1" t="inlineStr"/>
-      <c r="F52" s="1" t="inlineStr"/>
-      <c r="G52" s="1" t="inlineStr"/>
-      <c r="H52" s="1" t="inlineStr"/>
-      <c r="I52" s="1" t="inlineStr"/>
-      <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr"/>
-      <c r="L52" s="1" t="inlineStr"/>
-      <c r="M52" s="1" t="inlineStr"/>
+      <c r="B52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H52" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J52" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K52" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L52" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M52" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -1485,18 +3825,64 @@
           <t>3321145</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr"/>
-      <c r="C53" s="1" t="inlineStr"/>
-      <c r="D53" s="1" t="inlineStr"/>
-      <c r="E53" s="1" t="inlineStr"/>
-      <c r="F53" s="1" t="inlineStr"/>
-      <c r="G53" s="1" t="inlineStr"/>
-      <c r="H53" s="1" t="inlineStr"/>
-      <c r="I53" s="1" t="inlineStr"/>
-      <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr"/>
-      <c r="L53" s="1" t="inlineStr"/>
-      <c r="M53" s="1" t="inlineStr"/>
+      <c r="B53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J53" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K53" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L53" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M53" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -1504,18 +3890,64 @@
           <t>3321817</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr"/>
-      <c r="C54" s="1" t="inlineStr"/>
-      <c r="D54" s="1" t="inlineStr"/>
-      <c r="E54" s="1" t="inlineStr"/>
-      <c r="F54" s="1" t="inlineStr"/>
-      <c r="G54" s="1" t="inlineStr"/>
-      <c r="H54" s="1" t="inlineStr"/>
-      <c r="I54" s="1" t="inlineStr"/>
-      <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr"/>
-      <c r="L54" s="1" t="inlineStr"/>
-      <c r="M54" s="1" t="inlineStr"/>
+      <c r="B54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H54" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I54" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J54" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K54" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L54" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M54" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -1523,18 +3955,64 @@
           <t>3322177</t>
         </is>
       </c>
-      <c r="B55" s="1" t="inlineStr"/>
-      <c r="C55" s="1" t="inlineStr"/>
-      <c r="D55" s="1" t="inlineStr"/>
-      <c r="E55" s="1" t="inlineStr"/>
-      <c r="F55" s="1" t="inlineStr"/>
-      <c r="G55" s="1" t="inlineStr"/>
-      <c r="H55" s="1" t="inlineStr"/>
-      <c r="I55" s="1" t="inlineStr"/>
-      <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr"/>
-      <c r="L55" s="1" t="inlineStr"/>
-      <c r="M55" s="1" t="inlineStr"/>
+      <c r="B55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H55" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I55" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J55" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K55" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L55" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M55" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -1542,18 +4020,64 @@
           <t>3322370</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr"/>
-      <c r="C56" s="1" t="inlineStr"/>
-      <c r="D56" s="1" t="inlineStr"/>
-      <c r="E56" s="1" t="inlineStr"/>
-      <c r="F56" s="1" t="inlineStr"/>
-      <c r="G56" s="1" t="inlineStr"/>
-      <c r="H56" s="1" t="inlineStr"/>
-      <c r="I56" s="1" t="inlineStr"/>
-      <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr"/>
-      <c r="L56" s="1" t="inlineStr"/>
-      <c r="M56" s="1" t="inlineStr"/>
+      <c r="B56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L56" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M56" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -1561,18 +4085,64 @@
           <t>3323341</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr"/>
-      <c r="C57" s="1" t="inlineStr"/>
-      <c r="D57" s="1" t="inlineStr"/>
-      <c r="E57" s="1" t="inlineStr"/>
-      <c r="F57" s="1" t="inlineStr"/>
-      <c r="G57" s="1" t="inlineStr"/>
-      <c r="H57" s="1" t="inlineStr"/>
-      <c r="I57" s="1" t="inlineStr"/>
-      <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr"/>
-      <c r="L57" s="1" t="inlineStr"/>
-      <c r="M57" s="1" t="inlineStr"/>
+      <c r="B57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I57" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J57" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K57" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L57" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M57" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -1580,18 +4150,64 @@
           <t>3323555</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr"/>
-      <c r="C58" s="1" t="inlineStr"/>
-      <c r="D58" s="1" t="inlineStr"/>
-      <c r="E58" s="1" t="inlineStr"/>
-      <c r="F58" s="1" t="inlineStr"/>
-      <c r="G58" s="1" t="inlineStr"/>
-      <c r="H58" s="1" t="inlineStr"/>
-      <c r="I58" s="1" t="inlineStr"/>
-      <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr"/>
-      <c r="L58" s="1" t="inlineStr"/>
-      <c r="M58" s="1" t="inlineStr"/>
+      <c r="B58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I58" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J58" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K58" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L58" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M58" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -1599,18 +4215,64 @@
           <t>3323556</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr"/>
-      <c r="C59" s="1" t="inlineStr"/>
-      <c r="D59" s="1" t="inlineStr"/>
-      <c r="E59" s="1" t="inlineStr"/>
-      <c r="F59" s="1" t="inlineStr"/>
-      <c r="G59" s="1" t="inlineStr"/>
-      <c r="H59" s="1" t="inlineStr"/>
-      <c r="I59" s="1" t="inlineStr"/>
-      <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr"/>
-      <c r="L59" s="1" t="inlineStr"/>
-      <c r="M59" s="1" t="inlineStr"/>
+      <c r="B59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H59" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I59" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J59" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K59" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L59" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M59" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -1618,18 +4280,64 @@
           <t>3326967</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr"/>
-      <c r="C60" s="1" t="inlineStr"/>
-      <c r="D60" s="1" t="inlineStr"/>
-      <c r="E60" s="1" t="inlineStr"/>
-      <c r="F60" s="1" t="inlineStr"/>
-      <c r="G60" s="1" t="inlineStr"/>
-      <c r="H60" s="1" t="inlineStr"/>
-      <c r="I60" s="1" t="inlineStr"/>
-      <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr"/>
-      <c r="L60" s="1" t="inlineStr"/>
-      <c r="M60" s="1" t="inlineStr"/>
+      <c r="B60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H60" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I60" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J60" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K60" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L60" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M60" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -1637,18 +4345,64 @@
           <t>3327728</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr"/>
-      <c r="C61" s="1" t="inlineStr"/>
-      <c r="D61" s="1" t="inlineStr"/>
-      <c r="E61" s="1" t="inlineStr"/>
-      <c r="F61" s="1" t="inlineStr"/>
-      <c r="G61" s="1" t="inlineStr"/>
-      <c r="H61" s="1" t="inlineStr"/>
-      <c r="I61" s="1" t="inlineStr"/>
-      <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr"/>
-      <c r="L61" s="1" t="inlineStr"/>
-      <c r="M61" s="1" t="inlineStr"/>
+      <c r="B61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="H61" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="I61" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="J61" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="K61" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="L61" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="M61" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -1656,18 +4410,64 @@
           <t>3327949</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr"/>
-      <c r="C62" s="1" t="inlineStr"/>
-      <c r="D62" s="1" t="inlineStr"/>
-      <c r="E62" s="1" t="inlineStr"/>
-      <c r="F62" s="1" t="inlineStr"/>
-      <c r="G62" s="1" t="inlineStr"/>
-      <c r="H62" s="1" t="inlineStr"/>
-      <c r="I62" s="1" t="inlineStr"/>
-      <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr"/>
-      <c r="L62" s="1" t="inlineStr"/>
-      <c r="M62" s="1" t="inlineStr"/>
+      <c r="B62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H62" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I62" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J62" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K62" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L62" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M62" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -1675,18 +4475,64 @@
           <t>3327950</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr"/>
-      <c r="C63" s="1" t="inlineStr"/>
-      <c r="D63" s="1" t="inlineStr"/>
-      <c r="E63" s="1" t="inlineStr"/>
-      <c r="F63" s="1" t="inlineStr"/>
-      <c r="G63" s="1" t="inlineStr"/>
-      <c r="H63" s="1" t="inlineStr"/>
-      <c r="I63" s="1" t="inlineStr"/>
-      <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr"/>
-      <c r="L63" s="1" t="inlineStr"/>
-      <c r="M63" s="1" t="inlineStr"/>
+      <c r="B63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="H63" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="I63" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="J63" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="K63" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="L63" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="M63" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -1694,18 +4540,64 @@
           <t>3328102</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr"/>
-      <c r="C64" s="1" t="inlineStr"/>
-      <c r="D64" s="1" t="inlineStr"/>
-      <c r="E64" s="1" t="inlineStr"/>
-      <c r="F64" s="1" t="inlineStr"/>
-      <c r="G64" s="1" t="inlineStr"/>
-      <c r="H64" s="1" t="inlineStr"/>
-      <c r="I64" s="1" t="inlineStr"/>
-      <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr"/>
-      <c r="L64" s="1" t="inlineStr"/>
-      <c r="M64" s="1" t="inlineStr"/>
+      <c r="B64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H64" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I64" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J64" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K64" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L64" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M64" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1713,18 +4605,64 @@
           <t>3328120</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr"/>
-      <c r="C65" s="1" t="inlineStr"/>
-      <c r="D65" s="1" t="inlineStr"/>
-      <c r="E65" s="1" t="inlineStr"/>
-      <c r="F65" s="1" t="inlineStr"/>
-      <c r="G65" s="1" t="inlineStr"/>
-      <c r="H65" s="1" t="inlineStr"/>
-      <c r="I65" s="1" t="inlineStr"/>
-      <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr"/>
-      <c r="L65" s="1" t="inlineStr"/>
-      <c r="M65" s="1" t="inlineStr"/>
+      <c r="B65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G65" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H65" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I65" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J65" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K65" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L65" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M65" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -1732,18 +4670,64 @@
           <t>3328121</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr"/>
-      <c r="C66" s="1" t="inlineStr"/>
-      <c r="D66" s="1" t="inlineStr"/>
-      <c r="E66" s="1" t="inlineStr"/>
-      <c r="F66" s="1" t="inlineStr"/>
-      <c r="G66" s="1" t="inlineStr"/>
-      <c r="H66" s="1" t="inlineStr"/>
-      <c r="I66" s="1" t="inlineStr"/>
-      <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr"/>
-      <c r="L66" s="1" t="inlineStr"/>
-      <c r="M66" s="1" t="inlineStr"/>
+      <c r="B66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H66" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I66" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J66" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K66" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L66" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M66" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -1751,18 +4735,64 @@
           <t>3328588</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr"/>
-      <c r="C67" s="1" t="inlineStr"/>
-      <c r="D67" s="1" t="inlineStr"/>
-      <c r="E67" s="1" t="inlineStr"/>
-      <c r="F67" s="1" t="inlineStr"/>
-      <c r="G67" s="1" t="inlineStr"/>
-      <c r="H67" s="1" t="inlineStr"/>
-      <c r="I67" s="1" t="inlineStr"/>
-      <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr"/>
-      <c r="L67" s="1" t="inlineStr"/>
-      <c r="M67" s="1" t="inlineStr"/>
+      <c r="B67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F67" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H67" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I67" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J67" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K67" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L67" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M67" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -1770,18 +4800,58 @@
           <t>3328612</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr"/>
-      <c r="C68" s="1" t="inlineStr"/>
-      <c r="D68" s="1" t="inlineStr"/>
-      <c r="E68" s="1" t="inlineStr"/>
-      <c r="F68" s="1" t="inlineStr"/>
-      <c r="G68" s="1" t="inlineStr"/>
-      <c r="H68" s="1" t="inlineStr"/>
-      <c r="I68" s="1" t="inlineStr"/>
-      <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr"/>
-      <c r="L68" s="1" t="inlineStr"/>
-      <c r="M68" s="1" t="inlineStr"/>
+      <c r="B68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H68" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I68" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J68" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -1789,18 +4859,64 @@
           <t>3328642</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr"/>
-      <c r="C69" s="1" t="inlineStr"/>
-      <c r="D69" s="1" t="inlineStr"/>
-      <c r="E69" s="1" t="inlineStr"/>
-      <c r="F69" s="1" t="inlineStr"/>
-      <c r="G69" s="1" t="inlineStr"/>
-      <c r="H69" s="1" t="inlineStr"/>
-      <c r="I69" s="1" t="inlineStr"/>
-      <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr"/>
-      <c r="L69" s="1" t="inlineStr"/>
-      <c r="M69" s="1" t="inlineStr"/>
+      <c r="B69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="F69" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="G69" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="H69" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="I69" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="J69" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="K69" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="L69" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="M69" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -1808,18 +4924,64 @@
           <t>3328844</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr"/>
-      <c r="C70" s="1" t="inlineStr"/>
-      <c r="D70" s="1" t="inlineStr"/>
-      <c r="E70" s="1" t="inlineStr"/>
-      <c r="F70" s="1" t="inlineStr"/>
-      <c r="G70" s="1" t="inlineStr"/>
-      <c r="H70" s="1" t="inlineStr"/>
-      <c r="I70" s="1" t="inlineStr"/>
-      <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr"/>
-      <c r="L70" s="1" t="inlineStr"/>
-      <c r="M70" s="1" t="inlineStr"/>
+      <c r="B70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F70" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G70" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H70" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I70" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J70" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K70" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L70" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M70" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -1827,18 +4989,44 @@
           <t>3328845</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr"/>
-      <c r="C71" s="1" t="inlineStr"/>
-      <c r="D71" s="1" t="inlineStr"/>
-      <c r="E71" s="1" t="inlineStr"/>
-      <c r="F71" s="1" t="inlineStr"/>
-      <c r="G71" s="1" t="inlineStr"/>
-      <c r="H71" s="1" t="inlineStr"/>
-      <c r="I71" s="1" t="inlineStr"/>
-      <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr"/>
-      <c r="L71" s="1" t="inlineStr"/>
-      <c r="M71" s="1" t="inlineStr"/>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -1846,18 +5034,64 @@
           <t>3328957</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr"/>
-      <c r="C72" s="1" t="inlineStr"/>
-      <c r="D72" s="1" t="inlineStr"/>
-      <c r="E72" s="1" t="inlineStr"/>
-      <c r="F72" s="1" t="inlineStr"/>
-      <c r="G72" s="1" t="inlineStr"/>
-      <c r="H72" s="1" t="inlineStr"/>
-      <c r="I72" s="1" t="inlineStr"/>
-      <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr"/>
-      <c r="L72" s="1" t="inlineStr"/>
-      <c r="M72" s="1" t="inlineStr"/>
+      <c r="B72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F72" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G72" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H72" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I72" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J72" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K72" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L72" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M72" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -1865,18 +5099,64 @@
           <t>3329985</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr"/>
-      <c r="C73" s="1" t="inlineStr"/>
-      <c r="D73" s="1" t="inlineStr"/>
-      <c r="E73" s="1" t="inlineStr"/>
-      <c r="F73" s="1" t="inlineStr"/>
-      <c r="G73" s="1" t="inlineStr"/>
-      <c r="H73" s="1" t="inlineStr"/>
-      <c r="I73" s="1" t="inlineStr"/>
-      <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr"/>
-      <c r="L73" s="1" t="inlineStr"/>
-      <c r="M73" s="1" t="inlineStr"/>
+      <c r="B73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F73" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G73" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H73" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I73" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J73" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K73" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L73" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M73" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -1884,18 +5164,64 @@
           <t>3330001</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr"/>
-      <c r="C74" s="1" t="inlineStr"/>
-      <c r="D74" s="1" t="inlineStr"/>
-      <c r="E74" s="1" t="inlineStr"/>
-      <c r="F74" s="1" t="inlineStr"/>
-      <c r="G74" s="1" t="inlineStr"/>
-      <c r="H74" s="1" t="inlineStr"/>
-      <c r="I74" s="1" t="inlineStr"/>
-      <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr"/>
-      <c r="L74" s="1" t="inlineStr"/>
-      <c r="M74" s="1" t="inlineStr"/>
+      <c r="B74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F74" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G74" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H74" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I74" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J74" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K74" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L74" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M74" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -1903,18 +5229,64 @@
           <t>3330120</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr"/>
-      <c r="C75" s="1" t="inlineStr"/>
-      <c r="D75" s="1" t="inlineStr"/>
-      <c r="E75" s="1" t="inlineStr"/>
-      <c r="F75" s="1" t="inlineStr"/>
-      <c r="G75" s="1" t="inlineStr"/>
-      <c r="H75" s="1" t="inlineStr"/>
-      <c r="I75" s="1" t="inlineStr"/>
-      <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr"/>
-      <c r="L75" s="1" t="inlineStr"/>
-      <c r="M75" s="1" t="inlineStr"/>
+      <c r="B75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F75" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G75" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H75" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I75" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J75" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K75" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L75" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M75" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -1922,18 +5294,64 @@
           <t>3330325</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr"/>
-      <c r="C76" s="1" t="inlineStr"/>
-      <c r="D76" s="1" t="inlineStr"/>
-      <c r="E76" s="1" t="inlineStr"/>
-      <c r="F76" s="1" t="inlineStr"/>
-      <c r="G76" s="1" t="inlineStr"/>
-      <c r="H76" s="1" t="inlineStr"/>
-      <c r="I76" s="1" t="inlineStr"/>
-      <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr"/>
-      <c r="L76" s="1" t="inlineStr"/>
-      <c r="M76" s="1" t="inlineStr"/>
+      <c r="B76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F76" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G76" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H76" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I76" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J76" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K76" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L76" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M76" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -1941,18 +5359,64 @@
           <t>3330402</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr"/>
-      <c r="C77" s="1" t="inlineStr"/>
-      <c r="D77" s="1" t="inlineStr"/>
-      <c r="E77" s="1" t="inlineStr"/>
-      <c r="F77" s="1" t="inlineStr"/>
-      <c r="G77" s="1" t="inlineStr"/>
-      <c r="H77" s="1" t="inlineStr"/>
-      <c r="I77" s="1" t="inlineStr"/>
-      <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr"/>
-      <c r="L77" s="1" t="inlineStr"/>
-      <c r="M77" s="1" t="inlineStr"/>
+      <c r="B77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F77" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G77" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H77" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I77" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J77" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K77" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L77" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M77" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -1960,18 +5424,64 @@
           <t>3330651</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr"/>
-      <c r="C78" s="1" t="inlineStr"/>
-      <c r="D78" s="1" t="inlineStr"/>
-      <c r="E78" s="1" t="inlineStr"/>
-      <c r="F78" s="1" t="inlineStr"/>
-      <c r="G78" s="1" t="inlineStr"/>
-      <c r="H78" s="1" t="inlineStr"/>
-      <c r="I78" s="1" t="inlineStr"/>
-      <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr"/>
-      <c r="L78" s="1" t="inlineStr"/>
-      <c r="M78" s="1" t="inlineStr"/>
+      <c r="B78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F78" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G78" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H78" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I78" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J78" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K78" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L78" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M78" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -1979,18 +5489,64 @@
           <t>3330717</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr"/>
-      <c r="C79" s="1" t="inlineStr"/>
-      <c r="D79" s="1" t="inlineStr"/>
-      <c r="E79" s="1" t="inlineStr"/>
-      <c r="F79" s="1" t="inlineStr"/>
-      <c r="G79" s="1" t="inlineStr"/>
-      <c r="H79" s="1" t="inlineStr"/>
-      <c r="I79" s="1" t="inlineStr"/>
-      <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr"/>
-      <c r="L79" s="1" t="inlineStr"/>
-      <c r="M79" s="1" t="inlineStr"/>
+      <c r="B79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F79" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G79" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H79" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I79" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J79" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K79" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L79" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M79" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -1998,18 +5554,64 @@
           <t>3330759</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr"/>
-      <c r="C80" s="1" t="inlineStr"/>
-      <c r="D80" s="1" t="inlineStr"/>
-      <c r="E80" s="1" t="inlineStr"/>
-      <c r="F80" s="1" t="inlineStr"/>
-      <c r="G80" s="1" t="inlineStr"/>
-      <c r="H80" s="1" t="inlineStr"/>
-      <c r="I80" s="1" t="inlineStr"/>
-      <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr"/>
-      <c r="L80" s="1" t="inlineStr"/>
-      <c r="M80" s="1" t="inlineStr"/>
+      <c r="B80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G80" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H80" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I80" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J80" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K80" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L80" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M80" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -2017,18 +5619,64 @@
           <t>3331214</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr"/>
-      <c r="C81" s="1" t="inlineStr"/>
-      <c r="D81" s="1" t="inlineStr"/>
-      <c r="E81" s="1" t="inlineStr"/>
-      <c r="F81" s="1" t="inlineStr"/>
-      <c r="G81" s="1" t="inlineStr"/>
-      <c r="H81" s="1" t="inlineStr"/>
-      <c r="I81" s="1" t="inlineStr"/>
-      <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr"/>
-      <c r="L81" s="1" t="inlineStr"/>
-      <c r="M81" s="1" t="inlineStr"/>
+      <c r="B81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="E81" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="F81" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="G81" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="H81" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="I81" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="J81" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="K81" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="L81" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="M81" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -2036,18 +5684,64 @@
           <t>3331215</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr"/>
-      <c r="C82" s="1" t="inlineStr"/>
-      <c r="D82" s="1" t="inlineStr"/>
-      <c r="E82" s="1" t="inlineStr"/>
-      <c r="F82" s="1" t="inlineStr"/>
-      <c r="G82" s="1" t="inlineStr"/>
-      <c r="H82" s="1" t="inlineStr"/>
-      <c r="I82" s="1" t="inlineStr"/>
-      <c r="J82" s="1" t="inlineStr"/>
-      <c r="K82" s="1" t="inlineStr"/>
-      <c r="L82" s="1" t="inlineStr"/>
-      <c r="M82" s="1" t="inlineStr"/>
+      <c r="B82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F82" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G82" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H82" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I82" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J82" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K82" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L82" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M82" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -2055,18 +5749,64 @@
           <t>3331248</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr"/>
-      <c r="C83" s="1" t="inlineStr"/>
-      <c r="D83" s="1" t="inlineStr"/>
-      <c r="E83" s="1" t="inlineStr"/>
-      <c r="F83" s="1" t="inlineStr"/>
-      <c r="G83" s="1" t="inlineStr"/>
-      <c r="H83" s="1" t="inlineStr"/>
-      <c r="I83" s="1" t="inlineStr"/>
-      <c r="J83" s="1" t="inlineStr"/>
-      <c r="K83" s="1" t="inlineStr"/>
-      <c r="L83" s="1" t="inlineStr"/>
-      <c r="M83" s="1" t="inlineStr"/>
+      <c r="B83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F83" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G83" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I83" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J83" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K83" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L83" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M83" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -2074,18 +5814,64 @@
           <t>3331249</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr"/>
-      <c r="C84" s="1" t="inlineStr"/>
-      <c r="D84" s="1" t="inlineStr"/>
-      <c r="E84" s="1" t="inlineStr"/>
-      <c r="F84" s="1" t="inlineStr"/>
-      <c r="G84" s="1" t="inlineStr"/>
-      <c r="H84" s="1" t="inlineStr"/>
-      <c r="I84" s="1" t="inlineStr"/>
-      <c r="J84" s="1" t="inlineStr"/>
-      <c r="K84" s="1" t="inlineStr"/>
-      <c r="L84" s="1" t="inlineStr"/>
-      <c r="M84" s="1" t="inlineStr"/>
+      <c r="B84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E84" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F84" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G84" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H84" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I84" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J84" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K84" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L84" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M84" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -2093,18 +5879,64 @@
           <t>3331253</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr"/>
-      <c r="C85" s="1" t="inlineStr"/>
-      <c r="D85" s="1" t="inlineStr"/>
-      <c r="E85" s="1" t="inlineStr"/>
-      <c r="F85" s="1" t="inlineStr"/>
-      <c r="G85" s="1" t="inlineStr"/>
-      <c r="H85" s="1" t="inlineStr"/>
-      <c r="I85" s="1" t="inlineStr"/>
-      <c r="J85" s="1" t="inlineStr"/>
-      <c r="K85" s="1" t="inlineStr"/>
-      <c r="L85" s="1" t="inlineStr"/>
-      <c r="M85" s="1" t="inlineStr"/>
+      <c r="B85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E85" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F85" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G85" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H85" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I85" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J85" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K85" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L85" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M85" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -2112,18 +5944,64 @@
           <t>3331266</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr"/>
-      <c r="C86" s="1" t="inlineStr"/>
-      <c r="D86" s="1" t="inlineStr"/>
-      <c r="E86" s="1" t="inlineStr"/>
-      <c r="F86" s="1" t="inlineStr"/>
-      <c r="G86" s="1" t="inlineStr"/>
-      <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr"/>
-      <c r="J86" s="1" t="inlineStr"/>
-      <c r="K86" s="1" t="inlineStr"/>
-      <c r="L86" s="1" t="inlineStr"/>
-      <c r="M86" s="1" t="inlineStr"/>
+      <c r="B86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G86" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H86" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I86" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J86" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K86" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L86" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M86" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -2131,18 +6009,64 @@
           <t>3331529</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr"/>
-      <c r="C87" s="1" t="inlineStr"/>
-      <c r="D87" s="1" t="inlineStr"/>
-      <c r="E87" s="1" t="inlineStr"/>
-      <c r="F87" s="1" t="inlineStr"/>
-      <c r="G87" s="1" t="inlineStr"/>
-      <c r="H87" s="1" t="inlineStr"/>
-      <c r="I87" s="1" t="inlineStr"/>
-      <c r="J87" s="1" t="inlineStr"/>
-      <c r="K87" s="1" t="inlineStr"/>
-      <c r="L87" s="1" t="inlineStr"/>
-      <c r="M87" s="1" t="inlineStr"/>
+      <c r="B87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G87" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H87" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I87" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J87" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K87" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L87" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M87" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -2150,18 +6074,64 @@
           <t>3331644</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr"/>
-      <c r="C88" s="1" t="inlineStr"/>
-      <c r="D88" s="1" t="inlineStr"/>
-      <c r="E88" s="1" t="inlineStr"/>
-      <c r="F88" s="1" t="inlineStr"/>
-      <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr"/>
-      <c r="I88" s="1" t="inlineStr"/>
-      <c r="J88" s="1" t="inlineStr"/>
-      <c r="K88" s="1" t="inlineStr"/>
-      <c r="L88" s="1" t="inlineStr"/>
-      <c r="M88" s="1" t="inlineStr"/>
+      <c r="B88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F88" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G88" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H88" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I88" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J88" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K88" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L88" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M88" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -2169,18 +6139,64 @@
           <t>3331903</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr"/>
-      <c r="C89" s="1" t="inlineStr"/>
-      <c r="D89" s="1" t="inlineStr"/>
-      <c r="E89" s="1" t="inlineStr"/>
-      <c r="F89" s="1" t="inlineStr"/>
-      <c r="G89" s="1" t="inlineStr"/>
-      <c r="H89" s="1" t="inlineStr"/>
-      <c r="I89" s="1" t="inlineStr"/>
-      <c r="J89" s="1" t="inlineStr"/>
-      <c r="K89" s="1" t="inlineStr"/>
-      <c r="L89" s="1" t="inlineStr"/>
-      <c r="M89" s="1" t="inlineStr"/>
+      <c r="B89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F89" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G89" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H89" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I89" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J89" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K89" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L89" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M89" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -2188,18 +6204,64 @@
           <t>3332090</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr"/>
-      <c r="C90" s="1" t="inlineStr"/>
-      <c r="D90" s="1" t="inlineStr"/>
-      <c r="E90" s="1" t="inlineStr"/>
-      <c r="F90" s="1" t="inlineStr"/>
-      <c r="G90" s="1" t="inlineStr"/>
-      <c r="H90" s="1" t="inlineStr"/>
-      <c r="I90" s="1" t="inlineStr"/>
-      <c r="J90" s="1" t="inlineStr"/>
-      <c r="K90" s="1" t="inlineStr"/>
-      <c r="L90" s="1" t="inlineStr"/>
-      <c r="M90" s="1" t="inlineStr"/>
+      <c r="B90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H90" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I90" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J90" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K90" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L90" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M90" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -2207,18 +6269,64 @@
           <t>3332145</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr"/>
-      <c r="C91" s="1" t="inlineStr"/>
-      <c r="D91" s="1" t="inlineStr"/>
-      <c r="E91" s="1" t="inlineStr"/>
-      <c r="F91" s="1" t="inlineStr"/>
-      <c r="G91" s="1" t="inlineStr"/>
-      <c r="H91" s="1" t="inlineStr"/>
-      <c r="I91" s="1" t="inlineStr"/>
-      <c r="J91" s="1" t="inlineStr"/>
-      <c r="K91" s="1" t="inlineStr"/>
-      <c r="L91" s="1" t="inlineStr"/>
-      <c r="M91" s="1" t="inlineStr"/>
+      <c r="B91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G91" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H91" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I91" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J91" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K91" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L91" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M91" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -2226,18 +6334,64 @@
           <t>3332176</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr"/>
-      <c r="C92" s="1" t="inlineStr"/>
-      <c r="D92" s="1" t="inlineStr"/>
-      <c r="E92" s="1" t="inlineStr"/>
-      <c r="F92" s="1" t="inlineStr"/>
-      <c r="G92" s="1" t="inlineStr"/>
-      <c r="H92" s="1" t="inlineStr"/>
-      <c r="I92" s="1" t="inlineStr"/>
-      <c r="J92" s="1" t="inlineStr"/>
-      <c r="K92" s="1" t="inlineStr"/>
-      <c r="L92" s="1" t="inlineStr"/>
-      <c r="M92" s="1" t="inlineStr"/>
+      <c r="B92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F92" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G92" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H92" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I92" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J92" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K92" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L92" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M92" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -2245,18 +6399,64 @@
           <t>3332312</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr"/>
-      <c r="C93" s="1" t="inlineStr"/>
-      <c r="D93" s="1" t="inlineStr"/>
-      <c r="E93" s="1" t="inlineStr"/>
-      <c r="F93" s="1" t="inlineStr"/>
-      <c r="G93" s="1" t="inlineStr"/>
-      <c r="H93" s="1" t="inlineStr"/>
-      <c r="I93" s="1" t="inlineStr"/>
-      <c r="J93" s="1" t="inlineStr"/>
-      <c r="K93" s="1" t="inlineStr"/>
-      <c r="L93" s="1" t="inlineStr"/>
-      <c r="M93" s="1" t="inlineStr"/>
+      <c r="B93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E93" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F93" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G93" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H93" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I93" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J93" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K93" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L93" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M93" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -2264,18 +6464,64 @@
           <t>3332350</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr"/>
-      <c r="C94" s="1" t="inlineStr"/>
-      <c r="D94" s="1" t="inlineStr"/>
-      <c r="E94" s="1" t="inlineStr"/>
-      <c r="F94" s="1" t="inlineStr"/>
-      <c r="G94" s="1" t="inlineStr"/>
-      <c r="H94" s="1" t="inlineStr"/>
-      <c r="I94" s="1" t="inlineStr"/>
-      <c r="J94" s="1" t="inlineStr"/>
-      <c r="K94" s="1" t="inlineStr"/>
-      <c r="L94" s="1" t="inlineStr"/>
-      <c r="M94" s="1" t="inlineStr"/>
+      <c r="B94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E94" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F94" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G94" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H94" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I94" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J94" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K94" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L94" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M94" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -2283,18 +6529,64 @@
           <t>3332352</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr"/>
-      <c r="C95" s="1" t="inlineStr"/>
-      <c r="D95" s="1" t="inlineStr"/>
-      <c r="E95" s="1" t="inlineStr"/>
-      <c r="F95" s="1" t="inlineStr"/>
-      <c r="G95" s="1" t="inlineStr"/>
-      <c r="H95" s="1" t="inlineStr"/>
-      <c r="I95" s="1" t="inlineStr"/>
-      <c r="J95" s="1" t="inlineStr"/>
-      <c r="K95" s="1" t="inlineStr"/>
-      <c r="L95" s="1" t="inlineStr"/>
-      <c r="M95" s="1" t="inlineStr"/>
+      <c r="B95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F95" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G95" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H95" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I95" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J95" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K95" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L95" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M95" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -2302,18 +6594,64 @@
           <t>3332353</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr"/>
-      <c r="C96" s="1" t="inlineStr"/>
-      <c r="D96" s="1" t="inlineStr"/>
-      <c r="E96" s="1" t="inlineStr"/>
-      <c r="F96" s="1" t="inlineStr"/>
-      <c r="G96" s="1" t="inlineStr"/>
-      <c r="H96" s="1" t="inlineStr"/>
-      <c r="I96" s="1" t="inlineStr"/>
-      <c r="J96" s="1" t="inlineStr"/>
-      <c r="K96" s="1" t="inlineStr"/>
-      <c r="L96" s="1" t="inlineStr"/>
-      <c r="M96" s="1" t="inlineStr"/>
+      <c r="B96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="E96" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="F96" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="G96" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="H96" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="I96" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="J96" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="K96" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="L96" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
+      <c r="M96" s="1" t="inlineStr">
+        <is>
+          <t>B3 SERVIÇO PÚBLICO - AGUA, ESGOTO E SANE</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -2321,18 +6659,64 @@
           <t>3332495</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr"/>
-      <c r="C97" s="1" t="inlineStr"/>
-      <c r="D97" s="1" t="inlineStr"/>
-      <c r="E97" s="1" t="inlineStr"/>
-      <c r="F97" s="1" t="inlineStr"/>
-      <c r="G97" s="1" t="inlineStr"/>
-      <c r="H97" s="1" t="inlineStr"/>
-      <c r="I97" s="1" t="inlineStr"/>
-      <c r="J97" s="1" t="inlineStr"/>
-      <c r="K97" s="1" t="inlineStr"/>
-      <c r="L97" s="1" t="inlineStr"/>
-      <c r="M97" s="1" t="inlineStr"/>
+      <c r="B97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E97" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F97" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G97" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H97" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I97" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J97" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K97" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L97" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M97" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -2340,18 +6724,64 @@
           <t>3332699</t>
         </is>
       </c>
-      <c r="B98" s="1" t="inlineStr"/>
-      <c r="C98" s="1" t="inlineStr"/>
-      <c r="D98" s="1" t="inlineStr"/>
-      <c r="E98" s="1" t="inlineStr"/>
-      <c r="F98" s="1" t="inlineStr"/>
-      <c r="G98" s="1" t="inlineStr"/>
-      <c r="H98" s="1" t="inlineStr"/>
-      <c r="I98" s="1" t="inlineStr"/>
-      <c r="J98" s="1" t="inlineStr"/>
-      <c r="K98" s="1" t="inlineStr"/>
-      <c r="L98" s="1" t="inlineStr"/>
-      <c r="M98" s="1" t="inlineStr"/>
+      <c r="B98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E98" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F98" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G98" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H98" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I98" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J98" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K98" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L98" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M98" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -2359,18 +6789,64 @@
           <t>4129361</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr"/>
-      <c r="C99" s="1" t="inlineStr"/>
-      <c r="D99" s="1" t="inlineStr"/>
-      <c r="E99" s="1" t="inlineStr"/>
-      <c r="F99" s="1" t="inlineStr"/>
-      <c r="G99" s="1" t="inlineStr"/>
-      <c r="H99" s="1" t="inlineStr"/>
-      <c r="I99" s="1" t="inlineStr"/>
-      <c r="J99" s="1" t="inlineStr"/>
-      <c r="K99" s="1" t="inlineStr"/>
-      <c r="L99" s="1" t="inlineStr"/>
-      <c r="M99" s="1" t="inlineStr"/>
+      <c r="B99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E99" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F99" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G99" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H99" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I99" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J99" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K99" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L99" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M99" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -2378,18 +6854,64 @@
           <t>5402028</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr"/>
-      <c r="C100" s="1" t="inlineStr"/>
-      <c r="D100" s="1" t="inlineStr"/>
-      <c r="E100" s="1" t="inlineStr"/>
-      <c r="F100" s="1" t="inlineStr"/>
-      <c r="G100" s="1" t="inlineStr"/>
-      <c r="H100" s="1" t="inlineStr"/>
-      <c r="I100" s="1" t="inlineStr"/>
-      <c r="J100" s="1" t="inlineStr"/>
-      <c r="K100" s="1" t="inlineStr"/>
-      <c r="L100" s="1" t="inlineStr"/>
-      <c r="M100" s="1" t="inlineStr"/>
+      <c r="B100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E100" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F100" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G100" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H100" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I100" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J100" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K100" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L100" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M100" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -2397,18 +6919,64 @@
           <t>5604226</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr"/>
-      <c r="C101" s="1" t="inlineStr"/>
-      <c r="D101" s="1" t="inlineStr"/>
-      <c r="E101" s="1" t="inlineStr"/>
-      <c r="F101" s="1" t="inlineStr"/>
-      <c r="G101" s="1" t="inlineStr"/>
-      <c r="H101" s="1" t="inlineStr"/>
-      <c r="I101" s="1" t="inlineStr"/>
-      <c r="J101" s="1" t="inlineStr"/>
-      <c r="K101" s="1" t="inlineStr"/>
-      <c r="L101" s="1" t="inlineStr"/>
-      <c r="M101" s="1" t="inlineStr"/>
+      <c r="B101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E101" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F101" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G101" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H101" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I101" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J101" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K101" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L101" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M101" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -2416,18 +6984,64 @@
           <t>5722780</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr"/>
-      <c r="C102" s="1" t="inlineStr"/>
-      <c r="D102" s="1" t="inlineStr"/>
-      <c r="E102" s="1" t="inlineStr"/>
-      <c r="F102" s="1" t="inlineStr"/>
-      <c r="G102" s="1" t="inlineStr"/>
-      <c r="H102" s="1" t="inlineStr"/>
-      <c r="I102" s="1" t="inlineStr"/>
-      <c r="J102" s="1" t="inlineStr"/>
-      <c r="K102" s="1" t="inlineStr"/>
-      <c r="L102" s="1" t="inlineStr"/>
-      <c r="M102" s="1" t="inlineStr"/>
+      <c r="B102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E102" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F102" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G102" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H102" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I102" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J102" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K102" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L102" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M102" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -2435,18 +7049,64 @@
           <t>6055918</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr"/>
-      <c r="C103" s="1" t="inlineStr"/>
-      <c r="D103" s="1" t="inlineStr"/>
-      <c r="E103" s="1" t="inlineStr"/>
-      <c r="F103" s="1" t="inlineStr"/>
-      <c r="G103" s="1" t="inlineStr"/>
-      <c r="H103" s="1" t="inlineStr"/>
-      <c r="I103" s="1" t="inlineStr"/>
-      <c r="J103" s="1" t="inlineStr"/>
-      <c r="K103" s="1" t="inlineStr"/>
-      <c r="L103" s="1" t="inlineStr"/>
-      <c r="M103" s="1" t="inlineStr"/>
+      <c r="B103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E103" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F103" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G103" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H103" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I103" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J103" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K103" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L103" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M103" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -2454,18 +7114,64 @@
           <t>6056801</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr"/>
-      <c r="C104" s="1" t="inlineStr"/>
-      <c r="D104" s="1" t="inlineStr"/>
-      <c r="E104" s="1" t="inlineStr"/>
-      <c r="F104" s="1" t="inlineStr"/>
-      <c r="G104" s="1" t="inlineStr"/>
-      <c r="H104" s="1" t="inlineStr"/>
-      <c r="I104" s="1" t="inlineStr"/>
-      <c r="J104" s="1" t="inlineStr"/>
-      <c r="K104" s="1" t="inlineStr"/>
-      <c r="L104" s="1" t="inlineStr"/>
-      <c r="M104" s="1" t="inlineStr"/>
+      <c r="B104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E104" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F104" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G104" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H104" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I104" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J104" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K104" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L104" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M104" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -2473,18 +7179,64 @@
           <t>6056848</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr"/>
-      <c r="C105" s="1" t="inlineStr"/>
-      <c r="D105" s="1" t="inlineStr"/>
-      <c r="E105" s="1" t="inlineStr"/>
-      <c r="F105" s="1" t="inlineStr"/>
-      <c r="G105" s="1" t="inlineStr"/>
-      <c r="H105" s="1" t="inlineStr"/>
-      <c r="I105" s="1" t="inlineStr"/>
-      <c r="J105" s="1" t="inlineStr"/>
-      <c r="K105" s="1" t="inlineStr"/>
-      <c r="L105" s="1" t="inlineStr"/>
-      <c r="M105" s="1" t="inlineStr"/>
+      <c r="B105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I105" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J105" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K105" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L105" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M105" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -2492,18 +7244,64 @@
           <t>6060423</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr"/>
-      <c r="C106" s="1" t="inlineStr"/>
-      <c r="D106" s="1" t="inlineStr"/>
-      <c r="E106" s="1" t="inlineStr"/>
-      <c r="F106" s="1" t="inlineStr"/>
-      <c r="G106" s="1" t="inlineStr"/>
-      <c r="H106" s="1" t="inlineStr"/>
-      <c r="I106" s="1" t="inlineStr"/>
-      <c r="J106" s="1" t="inlineStr"/>
-      <c r="K106" s="1" t="inlineStr"/>
-      <c r="L106" s="1" t="inlineStr"/>
-      <c r="M106" s="1" t="inlineStr"/>
+      <c r="B106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E106" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F106" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G106" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H106" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I106" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J106" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K106" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L106" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M106" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -2511,18 +7309,64 @@
           <t>6636462</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr"/>
-      <c r="C107" s="1" t="inlineStr"/>
-      <c r="D107" s="1" t="inlineStr"/>
-      <c r="E107" s="1" t="inlineStr"/>
-      <c r="F107" s="1" t="inlineStr"/>
-      <c r="G107" s="1" t="inlineStr"/>
-      <c r="H107" s="1" t="inlineStr"/>
-      <c r="I107" s="1" t="inlineStr"/>
-      <c r="J107" s="1" t="inlineStr"/>
-      <c r="K107" s="1" t="inlineStr"/>
-      <c r="L107" s="1" t="inlineStr"/>
-      <c r="M107" s="1" t="inlineStr"/>
+      <c r="B107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E107" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F107" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G107" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H107" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I107" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J107" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K107" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L107" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M107" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -2530,18 +7374,64 @@
           <t>6819353</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr"/>
-      <c r="C108" s="1" t="inlineStr"/>
-      <c r="D108" s="1" t="inlineStr"/>
-      <c r="E108" s="1" t="inlineStr"/>
-      <c r="F108" s="1" t="inlineStr"/>
-      <c r="G108" s="1" t="inlineStr"/>
-      <c r="H108" s="1" t="inlineStr"/>
-      <c r="I108" s="1" t="inlineStr"/>
-      <c r="J108" s="1" t="inlineStr"/>
-      <c r="K108" s="1" t="inlineStr"/>
-      <c r="L108" s="1" t="inlineStr"/>
-      <c r="M108" s="1" t="inlineStr"/>
+      <c r="B108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E108" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F108" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G108" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H108" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I108" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J108" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K108" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L108" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M108" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -2549,18 +7439,64 @@
           <t>6819377</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr"/>
-      <c r="C109" s="1" t="inlineStr"/>
-      <c r="D109" s="1" t="inlineStr"/>
-      <c r="E109" s="1" t="inlineStr"/>
-      <c r="F109" s="1" t="inlineStr"/>
-      <c r="G109" s="1" t="inlineStr"/>
-      <c r="H109" s="1" t="inlineStr"/>
-      <c r="I109" s="1" t="inlineStr"/>
-      <c r="J109" s="1" t="inlineStr"/>
-      <c r="K109" s="1" t="inlineStr"/>
-      <c r="L109" s="1" t="inlineStr"/>
-      <c r="M109" s="1" t="inlineStr"/>
+      <c r="B109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E109" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F109" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G109" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H109" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I109" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J109" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K109" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L109" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M109" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -2568,18 +7504,64 @@
           <t>6819381</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr"/>
-      <c r="C110" s="1" t="inlineStr"/>
-      <c r="D110" s="1" t="inlineStr"/>
-      <c r="E110" s="1" t="inlineStr"/>
-      <c r="F110" s="1" t="inlineStr"/>
-      <c r="G110" s="1" t="inlineStr"/>
-      <c r="H110" s="1" t="inlineStr"/>
-      <c r="I110" s="1" t="inlineStr"/>
-      <c r="J110" s="1" t="inlineStr"/>
-      <c r="K110" s="1" t="inlineStr"/>
-      <c r="L110" s="1" t="inlineStr"/>
-      <c r="M110" s="1" t="inlineStr"/>
+      <c r="B110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E110" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F110" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H110" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I110" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J110" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K110" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L110" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M110" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -2587,18 +7569,64 @@
           <t>6819408</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr"/>
-      <c r="C111" s="1" t="inlineStr"/>
-      <c r="D111" s="1" t="inlineStr"/>
-      <c r="E111" s="1" t="inlineStr"/>
-      <c r="F111" s="1" t="inlineStr"/>
-      <c r="G111" s="1" t="inlineStr"/>
-      <c r="H111" s="1" t="inlineStr"/>
-      <c r="I111" s="1" t="inlineStr"/>
-      <c r="J111" s="1" t="inlineStr"/>
-      <c r="K111" s="1" t="inlineStr"/>
-      <c r="L111" s="1" t="inlineStr"/>
-      <c r="M111" s="1" t="inlineStr"/>
+      <c r="B111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E111" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F111" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G111" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H111" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I111" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J111" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K111" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L111" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M111" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -2606,18 +7634,64 @@
           <t>6819418</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr"/>
-      <c r="C112" s="1" t="inlineStr"/>
-      <c r="D112" s="1" t="inlineStr"/>
-      <c r="E112" s="1" t="inlineStr"/>
-      <c r="F112" s="1" t="inlineStr"/>
-      <c r="G112" s="1" t="inlineStr"/>
-      <c r="H112" s="1" t="inlineStr"/>
-      <c r="I112" s="1" t="inlineStr"/>
-      <c r="J112" s="1" t="inlineStr"/>
-      <c r="K112" s="1" t="inlineStr"/>
-      <c r="L112" s="1" t="inlineStr"/>
-      <c r="M112" s="1" t="inlineStr"/>
+      <c r="B112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D112" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E112" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F112" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G112" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H112" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I112" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J112" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K112" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L112" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M112" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -2625,18 +7699,64 @@
           <t>6941663</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr"/>
-      <c r="C113" s="1" t="inlineStr"/>
-      <c r="D113" s="1" t="inlineStr"/>
-      <c r="E113" s="1" t="inlineStr"/>
-      <c r="F113" s="1" t="inlineStr"/>
-      <c r="G113" s="1" t="inlineStr"/>
-      <c r="H113" s="1" t="inlineStr"/>
-      <c r="I113" s="1" t="inlineStr"/>
-      <c r="J113" s="1" t="inlineStr"/>
-      <c r="K113" s="1" t="inlineStr"/>
-      <c r="L113" s="1" t="inlineStr"/>
-      <c r="M113" s="1" t="inlineStr"/>
+      <c r="B113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E113" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F113" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G113" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H113" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I113" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J113" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K113" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L113" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M113" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -2644,18 +7764,64 @@
           <t>7133320</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr"/>
-      <c r="C114" s="1" t="inlineStr"/>
-      <c r="D114" s="1" t="inlineStr"/>
-      <c r="E114" s="1" t="inlineStr"/>
-      <c r="F114" s="1" t="inlineStr"/>
-      <c r="G114" s="1" t="inlineStr"/>
-      <c r="H114" s="1" t="inlineStr"/>
-      <c r="I114" s="1" t="inlineStr"/>
-      <c r="J114" s="1" t="inlineStr"/>
-      <c r="K114" s="1" t="inlineStr"/>
-      <c r="L114" s="1" t="inlineStr"/>
-      <c r="M114" s="1" t="inlineStr"/>
+      <c r="B114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D114" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E114" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F114" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G114" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H114" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I114" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J114" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K114" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L114" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M114" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -2663,18 +7829,64 @@
           <t>7133341</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr"/>
-      <c r="C115" s="1" t="inlineStr"/>
-      <c r="D115" s="1" t="inlineStr"/>
-      <c r="E115" s="1" t="inlineStr"/>
-      <c r="F115" s="1" t="inlineStr"/>
-      <c r="G115" s="1" t="inlineStr"/>
-      <c r="H115" s="1" t="inlineStr"/>
-      <c r="I115" s="1" t="inlineStr"/>
-      <c r="J115" s="1" t="inlineStr"/>
-      <c r="K115" s="1" t="inlineStr"/>
-      <c r="L115" s="1" t="inlineStr"/>
-      <c r="M115" s="1" t="inlineStr"/>
+      <c r="B115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D115" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E115" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F115" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G115" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H115" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I115" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J115" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K115" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L115" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M115" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -2682,18 +7894,64 @@
           <t>7133382</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr"/>
-      <c r="C116" s="1" t="inlineStr"/>
-      <c r="D116" s="1" t="inlineStr"/>
-      <c r="E116" s="1" t="inlineStr"/>
-      <c r="F116" s="1" t="inlineStr"/>
-      <c r="G116" s="1" t="inlineStr"/>
-      <c r="H116" s="1" t="inlineStr"/>
-      <c r="I116" s="1" t="inlineStr"/>
-      <c r="J116" s="1" t="inlineStr"/>
-      <c r="K116" s="1" t="inlineStr"/>
-      <c r="L116" s="1" t="inlineStr"/>
-      <c r="M116" s="1" t="inlineStr"/>
+      <c r="B116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D116" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E116" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F116" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G116" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H116" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I116" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J116" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K116" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L116" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M116" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -2701,18 +7959,64 @@
           <t>7133593</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr"/>
-      <c r="C117" s="1" t="inlineStr"/>
-      <c r="D117" s="1" t="inlineStr"/>
-      <c r="E117" s="1" t="inlineStr"/>
-      <c r="F117" s="1" t="inlineStr"/>
-      <c r="G117" s="1" t="inlineStr"/>
-      <c r="H117" s="1" t="inlineStr"/>
-      <c r="I117" s="1" t="inlineStr"/>
-      <c r="J117" s="1" t="inlineStr"/>
-      <c r="K117" s="1" t="inlineStr"/>
-      <c r="L117" s="1" t="inlineStr"/>
-      <c r="M117" s="1" t="inlineStr"/>
+      <c r="B117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D117" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E117" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F117" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G117" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H117" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I117" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J117" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K117" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L117" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M117" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -2720,18 +8024,64 @@
           <t>8056418</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr"/>
-      <c r="C118" s="1" t="inlineStr"/>
-      <c r="D118" s="1" t="inlineStr"/>
-      <c r="E118" s="1" t="inlineStr"/>
-      <c r="F118" s="1" t="inlineStr"/>
-      <c r="G118" s="1" t="inlineStr"/>
-      <c r="H118" s="1" t="inlineStr"/>
-      <c r="I118" s="1" t="inlineStr"/>
-      <c r="J118" s="1" t="inlineStr"/>
-      <c r="K118" s="1" t="inlineStr"/>
-      <c r="L118" s="1" t="inlineStr"/>
-      <c r="M118" s="1" t="inlineStr"/>
+      <c r="B118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E118" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F118" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H118" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I118" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J118" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K118" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L118" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M118" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -2739,18 +8089,64 @@
           <t>8056421</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr"/>
-      <c r="C119" s="1" t="inlineStr"/>
-      <c r="D119" s="1" t="inlineStr"/>
-      <c r="E119" s="1" t="inlineStr"/>
-      <c r="F119" s="1" t="inlineStr"/>
-      <c r="G119" s="1" t="inlineStr"/>
-      <c r="H119" s="1" t="inlineStr"/>
-      <c r="I119" s="1" t="inlineStr"/>
-      <c r="J119" s="1" t="inlineStr"/>
-      <c r="K119" s="1" t="inlineStr"/>
-      <c r="L119" s="1" t="inlineStr"/>
-      <c r="M119" s="1" t="inlineStr"/>
+      <c r="B119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E119" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F119" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G119" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H119" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I119" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J119" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K119" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L119" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M119" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -2758,18 +8154,64 @@
           <t>8132662</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr"/>
-      <c r="C120" s="1" t="inlineStr"/>
-      <c r="D120" s="1" t="inlineStr"/>
-      <c r="E120" s="1" t="inlineStr"/>
-      <c r="F120" s="1" t="inlineStr"/>
-      <c r="G120" s="1" t="inlineStr"/>
-      <c r="H120" s="1" t="inlineStr"/>
-      <c r="I120" s="1" t="inlineStr"/>
-      <c r="J120" s="1" t="inlineStr"/>
-      <c r="K120" s="1" t="inlineStr"/>
-      <c r="L120" s="1" t="inlineStr"/>
-      <c r="M120" s="1" t="inlineStr"/>
+      <c r="B120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E120" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F120" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I120" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J120" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K120" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L120" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M120" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -2777,18 +8219,64 @@
           <t>9057068</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr"/>
-      <c r="C121" s="1" t="inlineStr"/>
-      <c r="D121" s="1" t="inlineStr"/>
-      <c r="E121" s="1" t="inlineStr"/>
-      <c r="F121" s="1" t="inlineStr"/>
-      <c r="G121" s="1" t="inlineStr"/>
-      <c r="H121" s="1" t="inlineStr"/>
-      <c r="I121" s="1" t="inlineStr"/>
-      <c r="J121" s="1" t="inlineStr"/>
-      <c r="K121" s="1" t="inlineStr"/>
-      <c r="L121" s="1" t="inlineStr"/>
-      <c r="M121" s="1" t="inlineStr"/>
+      <c r="B121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E121" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F121" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G121" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H121" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I121" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J121" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K121" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L121" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M121" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -2796,18 +8284,64 @@
           <t>9061471</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr"/>
-      <c r="C122" s="1" t="inlineStr"/>
-      <c r="D122" s="1" t="inlineStr"/>
-      <c r="E122" s="1" t="inlineStr"/>
-      <c r="F122" s="1" t="inlineStr"/>
-      <c r="G122" s="1" t="inlineStr"/>
-      <c r="H122" s="1" t="inlineStr"/>
-      <c r="I122" s="1" t="inlineStr"/>
-      <c r="J122" s="1" t="inlineStr"/>
-      <c r="K122" s="1" t="inlineStr"/>
-      <c r="L122" s="1" t="inlineStr"/>
-      <c r="M122" s="1" t="inlineStr"/>
+      <c r="B122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="E122" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="F122" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="G122" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="H122" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="I122" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="J122" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="K122" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="L122" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
+      <c r="M122" s="1" t="inlineStr">
+        <is>
+          <t>B4a ILUMINAÇÃO PÚBLICA -ILUMINACAO PÚBL</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -2815,18 +8349,64 @@
           <t>9116003</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr"/>
-      <c r="C123" s="1" t="inlineStr"/>
-      <c r="D123" s="1" t="inlineStr"/>
-      <c r="E123" s="1" t="inlineStr"/>
-      <c r="F123" s="1" t="inlineStr"/>
-      <c r="G123" s="1" t="inlineStr"/>
-      <c r="H123" s="1" t="inlineStr"/>
-      <c r="I123" s="1" t="inlineStr"/>
-      <c r="J123" s="1" t="inlineStr"/>
-      <c r="K123" s="1" t="inlineStr"/>
-      <c r="L123" s="1" t="inlineStr"/>
-      <c r="M123" s="1" t="inlineStr"/>
+      <c r="B123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E123" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F123" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G123" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H123" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I123" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J123" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K123" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L123" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M123" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -2834,18 +8414,64 @@
           <t>9133801</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr"/>
-      <c r="C124" s="1" t="inlineStr"/>
-      <c r="D124" s="1" t="inlineStr"/>
-      <c r="E124" s="1" t="inlineStr"/>
-      <c r="F124" s="1" t="inlineStr"/>
-      <c r="G124" s="1" t="inlineStr"/>
-      <c r="H124" s="1" t="inlineStr"/>
-      <c r="I124" s="1" t="inlineStr"/>
-      <c r="J124" s="1" t="inlineStr"/>
-      <c r="K124" s="1" t="inlineStr"/>
-      <c r="L124" s="1" t="inlineStr"/>
-      <c r="M124" s="1" t="inlineStr"/>
+      <c r="B124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E124" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F124" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G124" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H124" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I124" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J124" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K124" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L124" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M124" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -2853,18 +8479,64 @@
           <t>9165621</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr"/>
-      <c r="C125" s="1" t="inlineStr"/>
-      <c r="D125" s="1" t="inlineStr"/>
-      <c r="E125" s="1" t="inlineStr"/>
-      <c r="F125" s="1" t="inlineStr"/>
-      <c r="G125" s="1" t="inlineStr"/>
-      <c r="H125" s="1" t="inlineStr"/>
-      <c r="I125" s="1" t="inlineStr"/>
-      <c r="J125" s="1" t="inlineStr"/>
-      <c r="K125" s="1" t="inlineStr"/>
-      <c r="L125" s="1" t="inlineStr"/>
-      <c r="M125" s="1" t="inlineStr"/>
+      <c r="B125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E125" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F125" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G125" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H125" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I125" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J125" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K125" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L125" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M125" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -2872,18 +8544,64 @@
           <t>9170342</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr"/>
-      <c r="C126" s="1" t="inlineStr"/>
-      <c r="D126" s="1" t="inlineStr"/>
-      <c r="E126" s="1" t="inlineStr"/>
-      <c r="F126" s="1" t="inlineStr"/>
-      <c r="G126" s="1" t="inlineStr"/>
-      <c r="H126" s="1" t="inlineStr"/>
-      <c r="I126" s="1" t="inlineStr"/>
-      <c r="J126" s="1" t="inlineStr"/>
-      <c r="K126" s="1" t="inlineStr"/>
-      <c r="L126" s="1" t="inlineStr"/>
-      <c r="M126" s="1" t="inlineStr"/>
+      <c r="B126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>B1 RESIDENCIAL -RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="inlineStr">
+        <is>
+          <t>B1 RESIDENCIAL -RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="E126" s="1" t="inlineStr">
+        <is>
+          <t>B1 RESIDENCIAL -RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="F126" s="1" t="inlineStr">
+        <is>
+          <t>B1 RESIDENCIAL -RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t>B1 RESIDENCIAL -RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="H126" s="1" t="inlineStr">
+        <is>
+          <t>B1 RESIDENCIAL -RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="I126" s="1" t="inlineStr">
+        <is>
+          <t>B1 RESIDENCIAL -RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="J126" s="1" t="inlineStr">
+        <is>
+          <t>B1 RESIDENCIAL -RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="K126" s="1" t="inlineStr">
+        <is>
+          <t>B1 RESIDENCIAL -RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="L126" s="1" t="inlineStr">
+        <is>
+          <t>B1 RESIDENCIAL -RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="M126" s="1" t="inlineStr">
+        <is>
+          <t>B1 RESIDENCIAL -RESIDENCIAL</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -2891,18 +8609,64 @@
           <t>994528</t>
         </is>
       </c>
-      <c r="B127" s="1" t="inlineStr"/>
-      <c r="C127" s="1" t="inlineStr"/>
-      <c r="D127" s="1" t="inlineStr"/>
-      <c r="E127" s="1" t="inlineStr"/>
-      <c r="F127" s="1" t="inlineStr"/>
-      <c r="G127" s="1" t="inlineStr"/>
-      <c r="H127" s="1" t="inlineStr"/>
-      <c r="I127" s="1" t="inlineStr"/>
-      <c r="J127" s="1" t="inlineStr"/>
-      <c r="K127" s="1" t="inlineStr"/>
-      <c r="L127" s="1" t="inlineStr"/>
-      <c r="M127" s="1" t="inlineStr"/>
+      <c r="B127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E127" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="F127" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="G127" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H127" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="I127" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="J127" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K127" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="L127" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="M127" s="1" t="inlineStr">
+        <is>
+          <t>B3 PODER PUBLICO -MUNICIPAL</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
